--- a/data/trans_dic/P2C_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Entrevistados que realiza cuidados a personas del hogar que lo requieren</t>
+          <t>Entrevistados que realiza cuidados a personas del hogar que lo requieren (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68,22; 83,13</t>
+          <t>68,12; 82,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,72; 93,54</t>
+          <t>80,16; 93,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,4; 83,65</t>
+          <t>65,59; 83,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,28; 31,72</t>
+          <t>18,01; 31,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,62; 79,03</t>
+          <t>62,33; 79,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,35; 92,7</t>
+          <t>80,83; 92,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,58; 88,98</t>
+          <t>74,68; 88,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,67; 33,91</t>
+          <t>19,63; 34,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>67,52; 79,07</t>
+          <t>68,08; 79,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82,79; 91,85</t>
+          <t>82,63; 91,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73,26; 84,55</t>
+          <t>73,29; 84,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,93; 30,56</t>
+          <t>21,1; 30,81</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,32; 82,2</t>
+          <t>63,34; 81,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87,79; 97,17</t>
+          <t>87,36; 97,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,35; 80,97</t>
+          <t>64,56; 80,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,79; 39,26</t>
+          <t>23,75; 39,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>67,95; 83,7</t>
+          <t>67,5; 84,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,94; 100,0</t>
+          <t>92,06; 99,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,76; 81,98</t>
+          <t>67,2; 81,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,19; 36,69</t>
+          <t>20,74; 36,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68,89; 80,78</t>
+          <t>68,13; 80,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91,77; 97,63</t>
+          <t>91,99; 97,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67,6; 79,15</t>
+          <t>67,98; 79,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,83; 35,66</t>
+          <t>23,7; 35,55</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50,5; 69,04</t>
+          <t>50,31; 71,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81,47; 93,84</t>
+          <t>81,2; 93,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,06; 80,99</t>
+          <t>57,55; 79,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,4; 47,41</t>
+          <t>22,33; 45,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58,48; 74,83</t>
+          <t>58,63; 74,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,11; 91,42</t>
+          <t>76,59; 91,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,59; 79,15</t>
+          <t>58,16; 77,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,0; 43,75</t>
+          <t>22,05; 42,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57,7; 70,55</t>
+          <t>57,72; 70,83</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81,06; 91,08</t>
+          <t>81,24; 90,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>61,65; 76,4</t>
+          <t>62,65; 76,72</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,19; 39,57</t>
+          <t>25,29; 40,78</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,26; 71,93</t>
+          <t>59,57; 72,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,6; 93,17</t>
+          <t>84,14; 92,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69,63; 80,34</t>
+          <t>69,08; 80,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,9; 32,77</t>
+          <t>16,28; 32,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>62,63; 74,95</t>
+          <t>62,12; 74,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,43; 90,05</t>
+          <t>81,23; 90,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,12; 81,89</t>
+          <t>70,75; 81,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,65; 35,36</t>
+          <t>23,46; 34,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,53; 71,36</t>
+          <t>62,45; 71,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84,32; 90,54</t>
+          <t>84,39; 90,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71,03; 79,49</t>
+          <t>71,13; 79,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,66; 31,74</t>
+          <t>20,37; 31,28</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>62,12; 80,31</t>
+          <t>63,15; 80,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>83,77; 94,23</t>
+          <t>84,19; 94,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70,44; 83,63</t>
+          <t>70,04; 83,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,64; 40,93</t>
+          <t>26,69; 41,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>61,19; 77,01</t>
+          <t>60,18; 76,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,61; 96,4</t>
+          <t>87,48; 96,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,49; 85,34</t>
+          <t>71,78; 85,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>32,72; 54,6</t>
+          <t>33,45; 54,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>64,25; 76,02</t>
+          <t>64,46; 75,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87,67; 94,49</t>
+          <t>88,05; 94,47</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73,16; 82,49</t>
+          <t>72,77; 82,6</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,24; 45,96</t>
+          <t>32,55; 46,56</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>61,87; 78,35</t>
+          <t>62,49; 78,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>83,44; 96,17</t>
+          <t>82,63; 96,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48,33; 69,97</t>
+          <t>48,3; 68,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29,84; 51,03</t>
+          <t>30,28; 51,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>51,29; 70,15</t>
+          <t>51,37; 70,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>70,0; 85,59</t>
+          <t>70,56; 86,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57,23; 76,49</t>
+          <t>57,71; 76,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37,76; 59,05</t>
+          <t>37,24; 59,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>59,57; 72,37</t>
+          <t>59,4; 72,03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78,22; 88,91</t>
+          <t>77,92; 88,7</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55,97; 70,49</t>
+          <t>56,0; 70,99</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36,88; 51,29</t>
+          <t>37,13; 52,71</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>66,6; 72,87</t>
+          <t>66,23; 72,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>87,35; 91,87</t>
+          <t>87,45; 92,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69,58; 76,25</t>
+          <t>69,63; 76,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24,98; 33,31</t>
+          <t>25,65; 33,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>65,3; 71,81</t>
+          <t>65,58; 72,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,48; 90,0</t>
+          <t>85,51; 90,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,74; 78,63</t>
+          <t>72,42; 78,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29,5; 37,21</t>
+          <t>29,64; 36,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>66,85; 71,74</t>
+          <t>66,83; 71,57</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87,02; 90,44</t>
+          <t>87,05; 90,48</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72,19; 76,71</t>
+          <t>72,04; 76,6</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,36; 33,98</t>
+          <t>28,54; 34,04</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Entrevistados que realiza cuidados a personas del hogar que lo requieren (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>61408</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>53784</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>48888</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25140</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>51161</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>64457</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>64542</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>36452</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>112568</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>118240</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>113430</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>61592</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>54809; 66773</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49078; 57266</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42521; 54399</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>18815; 33331</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>44653; 56634</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>59338; 67928</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>58443; 69419</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>26881; 46881</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>103543; 121266</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>111245; 123774</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>104873; 120471</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>50919; 74371</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>50592</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>61409</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>60594</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>29512</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>51660</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>66505</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>69301</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>26832</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>102253</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>127915</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>129895</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>56344</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>43510; 55718</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>57113; 64017</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>53139; 66470</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>22491; 37778</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>45553; 56753</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>63082; 67906</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>62543; 75634</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>19825; 35110</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>92770; 109334</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>123185; 130661</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>119225; 139025</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>45082; 67639</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>35225</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>58995</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>34437</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17324</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>56262</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>57579</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42331</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>20175</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>91487</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>116574</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>76768</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>37499</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>29306; 41435</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>54014; 62466</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28328; 39015</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11579; 23599</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>49215; 62672</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>52056; 62134</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>35487; 47558</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>14082; 27063</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>82074; 100709</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>109251; 122338</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>69057; 84570</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>29268; 47193</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>99956</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>121656</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>124572</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>54474</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>101884</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>139674</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>130779</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>62629</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>201840</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>261329</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>255351</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>117103</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>90120; 109603</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>114835; 126801</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>114531; 133550</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>35634; 70614</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>92280; 110415</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>131084; 145960</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>120904; 139706</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>51210; 76027</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>187259; 213573</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>251362; 269790</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>239494; 266994</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>89039; 136742</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>49917</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>84046</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>78716</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>40118</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>58347</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>85516</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>78243</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>66890</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>108263</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>169561</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>156958</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>107008</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>43652; 55855</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>78674; 88333</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>71150; 85157</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>31873; 49400</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>50874; 64635</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>80488; 88732</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>71168; 84632</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>54396; 87969</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>99041; 116187</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>163302; 175212</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>146066; 165810</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>91818; 131331</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>52951</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>49050</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>35778</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>27679</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>44507</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>58444</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>45814</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>34535</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>97457</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>107494</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>81592</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>62214</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>46784; 58797</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>44546; 51830</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>29143; 41400</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>20860; 35341</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>37188; 50721</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>52244; 63694</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>39140; 51947</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>26810; 42711</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>87479; 106080</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>99699; 113490</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>71770; 90985</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>52314; 74261</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1290</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>350047</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>428939</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>382985</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>194246</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>363821</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>472174</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>431009</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>247513</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>713868</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>901113</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>813994</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>441760</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>332913; 366154</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>417091; 439171</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>364897; 399986</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>168819; 218595</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>346609; 381488</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>459450; 483743</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>412928; 447509</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>222088; 277065</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>689159; 737998</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>882899; 917690</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>788357; 838201</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>401709; 479076</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2C_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68,12; 82,99</t>
+          <t>67,87; 83,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,16; 93,54</t>
+          <t>79,01; 93,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,59; 83,91</t>
+          <t>64,67; 84,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,01; 31,91</t>
+          <t>17,81; 31,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,33; 79,06</t>
+          <t>62,65; 80,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,83; 92,53</t>
+          <t>80,35; 92,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,68; 88,71</t>
+          <t>75,03; 89,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,63; 34,24</t>
+          <t>19,67; 34,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>68,08; 79,73</t>
+          <t>67,67; 79,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82,63; 91,94</t>
+          <t>83,01; 91,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73,29; 84,2</t>
+          <t>73,24; 84,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,1; 30,81</t>
+          <t>20,9; 30,63</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,34; 81,12</t>
+          <t>64,01; 81,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87,36; 97,92</t>
+          <t>88,37; 97,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,56; 80,76</t>
+          <t>65,04; 80,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,75; 39,9</t>
+          <t>23,52; 39,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>67,5; 84,1</t>
+          <t>67,29; 84,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,06; 99,1</t>
+          <t>92,0; 99,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,2; 81,27</t>
+          <t>65,87; 81,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,74; 36,74</t>
+          <t>21,11; 36,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68,13; 80,29</t>
+          <t>68,82; 81,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91,99; 97,58</t>
+          <t>91,8; 97,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67,98; 79,27</t>
+          <t>68,35; 79,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,7; 35,55</t>
+          <t>24,36; 35,87</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50,31; 71,14</t>
+          <t>49,5; 70,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81,2; 93,9</t>
+          <t>80,89; 94,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,55; 79,26</t>
+          <t>57,09; 79,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,33; 45,5</t>
+          <t>22,75; 45,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58,63; 74,66</t>
+          <t>58,65; 74,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,59; 91,42</t>
+          <t>76,13; 91,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,16; 77,95</t>
+          <t>59,09; 78,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,05; 42,38</t>
+          <t>21,98; 43,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57,72; 70,83</t>
+          <t>57,55; 70,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81,24; 90,97</t>
+          <t>80,78; 90,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62,65; 76,72</t>
+          <t>62,53; 76,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,29; 40,78</t>
+          <t>24,9; 40,09</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,57; 72,44</t>
+          <t>59,79; 72,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,14; 92,91</t>
+          <t>84,24; 92,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69,08; 80,55</t>
+          <t>69,01; 80,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,28; 32,27</t>
+          <t>16,9; 32,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>62,12; 74,32</t>
+          <t>62,4; 74,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,23; 90,45</t>
+          <t>80,81; 90,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,75; 81,76</t>
+          <t>70,29; 81,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,46; 34,83</t>
+          <t>23,41; 34,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,45; 71,22</t>
+          <t>62,92; 71,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84,39; 90,58</t>
+          <t>84,19; 90,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71,13; 79,3</t>
+          <t>71,54; 79,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,37; 31,28</t>
+          <t>21,43; 31,4</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>63,15; 80,81</t>
+          <t>62,33; 79,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>84,19; 94,52</t>
+          <t>84,09; 94,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70,04; 83,83</t>
+          <t>70,59; 84,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,69; 41,36</t>
+          <t>26,76; 41,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>60,18; 76,46</t>
+          <t>61,02; 76,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,48; 96,44</t>
+          <t>87,52; 96,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,78; 85,36</t>
+          <t>71,41; 84,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>33,45; 54,1</t>
+          <t>33,03; 54,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>64,46; 75,62</t>
+          <t>63,99; 75,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88,05; 94,47</t>
+          <t>87,82; 94,59</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,77; 82,6</t>
+          <t>72,82; 82,48</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,55; 46,56</t>
+          <t>32,22; 46,15</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62,49; 78,53</t>
+          <t>61,62; 78,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82,63; 96,14</t>
+          <t>83,19; 96,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48,3; 68,62</t>
+          <t>49,32; 70,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30,28; 51,3</t>
+          <t>30,53; 51,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>51,37; 70,06</t>
+          <t>51,67; 69,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>70,56; 86,03</t>
+          <t>70,68; 85,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57,71; 76,59</t>
+          <t>58,18; 76,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37,24; 59,32</t>
+          <t>37,61; 59,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>59,4; 72,03</t>
+          <t>59,62; 72,02</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>77,92; 88,7</t>
+          <t>78,53; 89,38</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56,0; 70,99</t>
+          <t>55,66; 70,29</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37,13; 52,71</t>
+          <t>36,81; 51,93</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>66,23; 72,84</t>
+          <t>65,97; 72,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>87,45; 92,08</t>
+          <t>87,71; 91,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69,63; 76,32</t>
+          <t>69,93; 76,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,65; 33,21</t>
+          <t>25,19; 33,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>65,58; 72,18</t>
+          <t>65,6; 72,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,51; 90,03</t>
+          <t>85,26; 90,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,42; 78,48</t>
+          <t>72,54; 78,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29,64; 36,98</t>
+          <t>29,86; 37,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>66,83; 71,57</t>
+          <t>66,87; 71,52</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87,05; 90,48</t>
+          <t>87,25; 90,39</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72,04; 76,6</t>
+          <t>72,36; 76,79</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,54; 34,04</t>
+          <t>28,65; 34,13</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>54809; 66773</t>
+          <t>54601; 67118</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>49078; 57266</t>
+          <t>48368; 57389</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42521; 54399</t>
+          <t>41927; 54556</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18815; 33331</t>
+          <t>18600; 32704</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>44653; 56634</t>
+          <t>44877; 57323</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>59338; 67928</t>
+          <t>58982; 67927</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58443; 69419</t>
+          <t>58717; 69771</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26881; 46881</t>
+          <t>26929; 46862</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>103543; 121266</t>
+          <t>102923; 121429</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>111245; 123774</t>
+          <t>111751; 123628</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>104873; 120471</t>
+          <t>104789; 121081</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50919; 74371</t>
+          <t>50457; 73927</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43510; 55718</t>
+          <t>43965; 55842</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57113; 64017</t>
+          <t>57777; 63983</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53139; 66470</t>
+          <t>53535; 66574</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22491; 37778</t>
+          <t>22266; 37310</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45553; 56753</t>
+          <t>45408; 56856</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63082; 67906</t>
+          <t>63044; 67898</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62543; 75634</t>
+          <t>61301; 75661</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19825; 35110</t>
+          <t>20175; 35300</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>92770; 109334</t>
+          <t>93711; 110635</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>123185; 130661</t>
+          <t>122920; 130798</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>119225; 139025</t>
+          <t>119866; 138715</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>45082; 67639</t>
+          <t>46338; 68243</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29306; 41435</t>
+          <t>28831; 41149</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>54014; 62466</t>
+          <t>53809; 62540</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28328; 39015</t>
+          <t>28100; 39051</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11579; 23599</t>
+          <t>11797; 23723</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>49215; 62672</t>
+          <t>49232; 62908</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>52056; 62134</t>
+          <t>51744; 62102</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35487; 47558</t>
+          <t>36053; 48008</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14082; 27063</t>
+          <t>14032; 27480</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>82074; 100709</t>
+          <t>81837; 100286</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>109251; 122338</t>
+          <t>108634; 122051</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69057; 84570</t>
+          <t>68926; 84457</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29268; 47193</t>
+          <t>28813; 46389</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>90120; 109603</t>
+          <t>90459; 109346</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>114835; 126801</t>
+          <t>114974; 126080</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>114531; 133550</t>
+          <t>114420; 132865</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35634; 70614</t>
+          <t>36986; 70023</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>92280; 110415</t>
+          <t>92702; 111195</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>131084; 145960</t>
+          <t>130402; 145808</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>120904; 139706</t>
+          <t>120106; 139521</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51210; 76027</t>
+          <t>51107; 75546</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>187259; 213573</t>
+          <t>188656; 214226</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>251362; 269790</t>
+          <t>250760; 269538</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>239494; 266994</t>
+          <t>240856; 267080</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>89039; 136742</t>
+          <t>93667; 137269</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43652; 55855</t>
+          <t>43083; 55152</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>78674; 88333</t>
+          <t>78587; 88476</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71150; 85157</t>
+          <t>71706; 85440</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31873; 49400</t>
+          <t>31965; 49131</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>50874; 64635</t>
+          <t>51579; 64302</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80488; 88732</t>
+          <t>80528; 88737</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>71168; 84632</t>
+          <t>70805; 83996</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>54396; 87969</t>
+          <t>53705; 88580</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>99041; 116187</t>
+          <t>98322; 116374</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>163302; 175212</t>
+          <t>162864; 175430</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>146066; 165810</t>
+          <t>146164; 165559</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>91818; 131331</t>
+          <t>90868; 130172</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46784; 58797</t>
+          <t>46136; 58866</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>44546; 51830</t>
+          <t>44846; 51854</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29143; 41400</t>
+          <t>29754; 42246</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20860; 35341</t>
+          <t>21036; 35417</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37188; 50721</t>
+          <t>37407; 50634</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52244; 63694</t>
+          <t>52328; 63265</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39140; 51947</t>
+          <t>39460; 51763</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>26810; 42711</t>
+          <t>27077; 43152</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>87479; 106080</t>
+          <t>87794; 106060</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>99699; 113490</t>
+          <t>100481; 114364</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>71770; 90985</t>
+          <t>71333; 90081</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>52314; 74261</t>
+          <t>51866; 73170</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>332913; 366154</t>
+          <t>331600; 365980</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>417091; 439171</t>
+          <t>418324; 438557</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>364897; 399986</t>
+          <t>366503; 399859</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>168819; 218595</t>
+          <t>165817; 218657</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>346609; 381488</t>
+          <t>346730; 380608</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>459450; 483743</t>
+          <t>458125; 483747</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>412928; 447509</t>
+          <t>413604; 448191</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>222088; 277065</t>
+          <t>223745; 278367</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>689159; 737998</t>
+          <t>689566; 737493</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>882899; 917690</t>
+          <t>884932; 916801</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>788357; 838201</t>
+          <t>791865; 840237</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>401709; 479076</t>
+          <t>403175; 480390</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>71,42%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>87,8%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>82,48%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28,77%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>76,33%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>87,85%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>75,41%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24,07%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>71,42%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>87,8%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>82,48%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>67,87; 83,42</t>
+          <t>61,62; 79,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,01; 93,74</t>
+          <t>80,35; 92,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,67; 84,15</t>
+          <t>74,58; 88,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,81; 31,31</t>
+          <t>21,89; 36,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,65; 80,02</t>
+          <t>68,22; 83,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,35; 92,53</t>
+          <t>80,72; 93,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,03; 89,16</t>
+          <t>65,4; 83,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,67; 34,23</t>
+          <t>18,39; 32,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>67,67; 79,84</t>
+          <t>67,52; 79,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83,01; 91,83</t>
+          <t>82,79; 91,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73,24; 84,62</t>
+          <t>73,26; 84,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,9; 30,63</t>
+          <t>22,27; 32,25</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>76,55%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>97,05%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>74,46%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28,67%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>73,66%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>93,93%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>73,62%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>31,17%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>76,55%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>74,46%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,01; 81,3</t>
+          <t>67,95; 83,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88,37; 97,87</t>
+          <t>91,94; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65,04; 80,88</t>
+          <t>66,76; 81,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,52; 39,41</t>
+          <t>20,65; 37,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>67,29; 84,25</t>
+          <t>63,32; 82,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,0; 99,08</t>
+          <t>87,79; 97,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,87; 81,3</t>
+          <t>64,35; 80,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,11; 36,93</t>
+          <t>24,04; 40,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68,82; 81,25</t>
+          <t>68,89; 80,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91,8; 97,68</t>
+          <t>91,77; 97,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68,35; 79,09</t>
+          <t>67,6; 79,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,36; 35,87</t>
+          <t>24,5; 36,41</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>67,02%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>84,72%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>69,38%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>31,94%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>60,48%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>88,68%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>69,96%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>33,4%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>67,02%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,72%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,38%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>33,28%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,5; 70,65</t>
+          <t>58,48; 74,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80,89; 94,01</t>
+          <t>76,11; 91,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,09; 79,33</t>
+          <t>58,59; 79,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,75; 45,74</t>
+          <t>22,24; 44,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58,65; 74,94</t>
+          <t>50,5; 69,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,13; 91,37</t>
+          <t>81,47; 93,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,09; 78,69</t>
+          <t>59,06; 80,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,98; 43,04</t>
+          <t>23,57; 49,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57,55; 70,53</t>
+          <t>57,7; 70,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80,78; 90,75</t>
+          <t>81,06; 91,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62,53; 76,62</t>
+          <t>61,65; 76,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,9; 40,09</t>
+          <t>25,68; 41,55</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>68,58%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>86,56%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>76,53%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28,9%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>66,07%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>89,14%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>75,14%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24,89%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>68,58%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>86,56%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>76,53%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,79; 72,27</t>
+          <t>62,63; 74,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,24; 92,38</t>
+          <t>81,43; 90,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69,01; 80,14</t>
+          <t>71,12; 81,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,9; 32,0</t>
+          <t>23,81; 35,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>62,4; 74,85</t>
+          <t>59,26; 71,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,81; 90,36</t>
+          <t>84,6; 93,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,29; 81,65</t>
+          <t>69,63; 80,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,41; 34,61</t>
+          <t>21,55; 32,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,92; 71,44</t>
+          <t>62,53; 71,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84,19; 90,5</t>
+          <t>84,32; 90,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71,54; 79,33</t>
+          <t>71,03; 79,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,43; 31,4</t>
+          <t>24,25; 32,36</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>69,03%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>92,94%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>78,91%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>41,63%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>72,21%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>89,94%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>77,49%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>33,59%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>69,03%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>92,94%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>78,91%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,8%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>62,33; 79,79</t>
+          <t>61,19; 77,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>84,09; 94,68</t>
+          <t>87,61; 96,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70,59; 84,11</t>
+          <t>71,49; 85,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,76; 41,14</t>
+          <t>33,17; 53,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>61,02; 76,07</t>
+          <t>62,12; 80,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,52; 96,45</t>
+          <t>83,77; 94,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,41; 84,71</t>
+          <t>70,44; 83,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>33,03; 54,47</t>
+          <t>28,65; 42,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>63,99; 75,74</t>
+          <t>64,25; 76,02</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87,82; 94,59</t>
+          <t>87,67; 94,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,82; 82,48</t>
+          <t>73,16; 82,49</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,22; 46,15</t>
+          <t>33,3; 46,35</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>61,48%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>78,94%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>67,55%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>50,6%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>70,72%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>90,98%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>59,3%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>40,18%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>61,48%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>78,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>67,55%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,52%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>61,62; 78,62</t>
+          <t>51,29; 70,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>83,19; 96,18</t>
+          <t>70,0; 85,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49,32; 70,02</t>
+          <t>57,23; 76,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30,53; 51,41</t>
+          <t>40,41; 61,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>51,67; 69,94</t>
+          <t>61,87; 78,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>70,68; 85,45</t>
+          <t>83,44; 96,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58,18; 76,32</t>
+          <t>48,33; 69,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37,61; 59,93</t>
+          <t>28,39; 49,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>59,62; 72,02</t>
+          <t>59,57; 72,37</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78,53; 89,38</t>
+          <t>78,22; 88,91</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55,66; 70,29</t>
+          <t>55,97; 70,49</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36,81; 51,93</t>
+          <t>37,02; 51,86</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>68,83%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>87,88%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>75,59%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>33,98%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>69,64%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>89,93%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>73,08%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>29,51%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>68,83%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>87,88%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>75,59%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>65,97; 72,81</t>
+          <t>65,3; 71,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>87,71; 91,95</t>
+          <t>85,48; 90,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69,93; 76,3</t>
+          <t>72,74; 78,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,19; 33,22</t>
+          <t>30,45; 38,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>65,6; 72,01</t>
+          <t>66,6; 72,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,26; 90,03</t>
+          <t>87,35; 91,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,54; 78,6</t>
+          <t>69,58; 76,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29,86; 37,15</t>
+          <t>27,78; 34,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>66,87; 71,52</t>
+          <t>66,85; 71,74</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87,25; 90,39</t>
+          <t>87,02; 90,44</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72,36; 76,79</t>
+          <t>72,19; 76,71</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,65; 34,13</t>
+          <t>29,93; 35,09</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>51161</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64457</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>64542</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>35260</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>61408</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>53784</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>48888</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25140</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>51161</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>64457</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>64542</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36452</t>
+          <t>25182</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61592</t>
+          <t>60442</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>54601; 67118</t>
+          <t>44142; 56616</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48368; 57389</t>
+          <t>58987; 68050</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41927; 54556</t>
+          <t>58365; 69631</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18600; 32704</t>
+          <t>26830; 44550</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>44877; 57323</t>
+          <t>54884; 66883</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58982; 67927</t>
+          <t>49420; 57263</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58717; 69771</t>
+          <t>42397; 54234</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26929; 46862</t>
+          <t>18924; 33089</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>102923; 121429</t>
+          <t>102695; 120254</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>111751; 123628</t>
+          <t>111466; 123661</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>104789; 121081</t>
+          <t>104825; 120976</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50457; 73927</t>
+          <t>50213; 72735</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>41</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>51660</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>66505</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>69301</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>26208</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>50592</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>61409</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>60594</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>29512</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>51660</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>66505</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69301</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26832</t>
+          <t>30787</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>56344</t>
+          <t>56994</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43965; 55842</t>
+          <t>45853; 56484</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57777; 63983</t>
+          <t>63003; 68526</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53535; 66574</t>
+          <t>62132; 76298</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22266; 37310</t>
+          <t>18872; 34278</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45408; 56856</t>
+          <t>43493; 56463</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63044; 67898</t>
+          <t>57395; 63528</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61301; 75661</t>
+          <t>52964; 66647</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20175; 35300</t>
+          <t>23205; 38735</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93711; 110635</t>
+          <t>93806; 109998</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>122920; 130798</t>
+          <t>122878; 130735</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>119866; 138715</t>
+          <t>118554; 138819</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46338; 68243</t>
+          <t>46038; 68429</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>56262</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>57579</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>42331</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>18188</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>35225</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>58995</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>34437</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>17324</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>56262</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>57579</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>42331</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20175</t>
+          <t>18562</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37499</t>
+          <t>36750</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>28831; 41149</t>
+          <t>49094; 62819</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>53809; 62540</t>
+          <t>51725; 62135</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28100; 39051</t>
+          <t>35746; 48292</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11797; 23723</t>
+          <t>12664; 25131</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>49232; 62908</t>
+          <t>29414; 40211</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51744; 62102</t>
+          <t>54195; 62425</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36053; 48008</t>
+          <t>29071; 39867</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14032; 27480</t>
+          <t>12605; 26658</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>81837; 100286</t>
+          <t>82047; 100316</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>108634; 122051</t>
+          <t>109017; 122486</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68926; 84457</t>
+          <t>67956; 84218</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28813; 46389</t>
+          <t>28358; 45886</t>
         </is>
       </c>
     </row>
@@ -2420,37 +2420,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>79</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>101884</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>139674</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>130779</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>58367</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>99956</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>121656</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>124572</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>54474</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>101884</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>139674</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>130779</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>62629</t>
+          <t>47752</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>117103</t>
+          <t>106119</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>90459; 109346</t>
+          <t>93045; 111341</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>114974; 126080</t>
+          <t>131407; 145303</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>114420; 132865</t>
+          <t>121533; 139939</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36986; 70023</t>
+          <t>48074; 71728</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>92702; 111195</t>
+          <t>89663; 108824</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>130402; 145808</t>
+          <t>115459; 127165</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>120106; 139521</t>
+          <t>115449; 133208</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51107; 75546</t>
+          <t>38709; 58412</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>188656; 214226</t>
+          <t>187513; 213967</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>250760; 269538</t>
+          <t>251128; 269656</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>240856; 267080</t>
+          <t>239153; 267623</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>93667; 137269</t>
+          <t>92522; 123470</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>119</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>121</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>66</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>58347</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>85516</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>78243</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>61714</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>49917</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>84046</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>78716</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>40118</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>58347</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>85516</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>78243</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>66890</t>
+          <t>41880</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>107008</t>
+          <t>103594</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43083; 55152</t>
+          <t>51724; 65096</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>78587; 88476</t>
+          <t>80607; 88696</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71706; 85440</t>
+          <t>70886; 84616</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31965; 49131</t>
+          <t>49171; 79389</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>51579; 64302</t>
+          <t>42942; 55510</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80528; 88737</t>
+          <t>78282; 88058</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>70805; 83996</t>
+          <t>71556; 84952</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>53705; 88580</t>
+          <t>34019; 50685</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>98322; 116374</t>
+          <t>98728; 116813</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>162864; 175430</t>
+          <t>162600; 175232</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>146164; 165559</t>
+          <t>146860; 165575</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>90868; 130172</t>
+          <t>88912; 123750</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>44507</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>58444</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>45814</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>34551</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>52951</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>49050</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>35778</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>27679</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>44507</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>58444</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>45814</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>34535</t>
+          <t>27171</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>62214</t>
+          <t>61722</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46136; 58866</t>
+          <t>37132; 50785</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>44846; 51854</t>
+          <t>51824; 63366</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29754; 42246</t>
+          <t>38819; 51878</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21036; 35417</t>
+          <t>27598; 42204</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37407; 50634</t>
+          <t>46322; 58660</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52328; 63265</t>
+          <t>44985; 51847</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39460; 51763</t>
+          <t>29162; 42216</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>27077; 43152</t>
+          <t>19971; 34989</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>87794; 106060</t>
+          <t>87720; 106581</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>100481; 114364</t>
+          <t>100079; 113757</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>71333; 90081</t>
+          <t>71733; 90339</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>51866; 73170</t>
+          <t>51322; 71896</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>519</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>290</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>363821</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>472174</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>431009</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>234287</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>350047</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>428939</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>382985</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>194246</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>363821</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>472174</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>431009</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>247513</t>
+          <t>191334</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>441760</t>
+          <t>425621</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>331600; 365980</t>
+          <t>345138; 379567</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>418324; 438557</t>
+          <t>459319; 483580</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>366503; 399859</t>
+          <t>414764; 448338</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>165817; 218657</t>
+          <t>209941; 262848</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>346730; 380608</t>
+          <t>334787; 366319</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>458125; 483747</t>
+          <t>416621; 438190</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>413604; 448191</t>
+          <t>364676; 399602</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>223745; 278367</t>
+          <t>172728; 212921</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>689566; 737493</t>
+          <t>689385; 739757</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>884932; 916801</t>
+          <t>882640; 917356</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>791865; 840237</t>
+          <t>790005; 839386</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>403175; 480390</t>
+          <t>392438; 460018</t>
         </is>
       </c>
     </row>
